--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a80410d6fdd5b9/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{9A4E9C85-CBF0-417D-95E3-2D2C58741EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{190BA7B5-3AF8-43DA-B915-700AC36029CD}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{9A4E9C85-CBF0-417D-95E3-2D2C58741EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECC368F2-45B6-4FE3-92AF-D11350864D15}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F73A646-9EE3-43C1-94FD-37A23BDC014F}"/>
   </bookViews>
@@ -388,10 +388,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -915,7 +911,7 @@
     </row>
     <row r="9" spans="1:7" s="1" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>12</v>
@@ -939,7 +935,7 @@
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>30</v>
@@ -963,7 +959,7 @@
     </row>
     <row r="11" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>33</v>
@@ -987,7 +983,7 @@
     </row>
     <row r="12" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>33</v>
@@ -1011,7 +1007,7 @@
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>33</v>
@@ -1036,7 +1032,7 @@
     </row>
     <row r="14" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>33</v>
@@ -1060,7 +1056,7 @@
     </row>
     <row r="15" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>40</v>
@@ -1084,7 +1080,7 @@
     </row>
     <row r="16" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>43</v>
@@ -1108,7 +1104,7 @@
     </row>
     <row r="17" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>46</v>
@@ -1132,7 +1128,7 @@
     </row>
     <row r="18" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>49</v>
@@ -1156,7 +1152,7 @@
     </row>
     <row r="19" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>13</v>
@@ -1180,7 +1176,7 @@
     </row>
     <row r="20" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>53</v>
@@ -1204,7 +1200,7 @@
     </row>
     <row r="21" spans="1:7" s="1" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>56</v>
@@ -1228,7 +1224,7 @@
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>59</v>
